--- a/assets/constructions/examples/ctd_mih_fe.xlsx
+++ b/assets/constructions/examples/ctd_mih_fe.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,11 +589,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R216-30EH25</t>
+          <t>R216-20EH20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -607,21 +627,21 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>24.2</v>
+        <v>19.3</v>
       </c>
       <c r="F2" t="n">
-        <v>24.2</v>
+        <v>19.3</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
@@ -636,14 +656,14 @@
         <v>12700</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="P2" t="n">
-        <v>26.9</v>
+        <v>17.9</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CoroMill 216 (R216-3006)</t>
+          <t>CoroMill 216 (R216-20T3)</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -657,12 +677,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>METRIC_EH:25</t>
+          <t>METRIC_EH:20</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>COR_R216:30H</t>
+          <t>COR_R216:20H</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -673,16 +693,16 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>E25</t>
+          <t>E20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>24.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>COR_R216-3006_H</t>
+          <t>COR_R216-20T3_H</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -699,39 +719,43 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R216-16EH16</t>
+          <t>RCF-20-10R-M10-2T</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CoroMillⓇ 216 ball nose milling cutter</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>15.5</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>25</v>
-      </c>
+      <c r="H3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -739,40 +763,36 @@
       <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="M3" t="n">
-        <v>85</v>
-      </c>
-      <c r="N3" t="n">
-        <v>12700</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="P3" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CoroMill 216 (R216-1603)</t>
+          <t>ZCEW100CE/ZCEW100SE</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>METRIC_EH:16</t>
+          <t>METRIC_THREAD:M10</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>COR_R216:16H</t>
+          <t>DER_ZCEW100H</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -783,21 +803,19 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>M10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>15.5</v>
-      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>COR_R216-1603_H</t>
+          <t>ZC10*_H</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -806,44 +824,56 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>204.49</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>16762.84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCM D25-M12</t>
+          <t>R216-20T10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DROP MILL</t>
+          <t>CoroMillⓇ 216 ball nose milling cutter</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
-      </c>
-      <c r="G4" t="n">
-        <v>68</v>
-      </c>
+        <v>17.8</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="J4" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -851,36 +881,40 @@
       <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>85</v>
+      </c>
+      <c r="N4" t="n">
+        <v>12700</v>
+      </c>
       <c r="O4" t="n">
-        <v>0.12</v>
+        <v>0.142</v>
       </c>
       <c r="P4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>BCR D250-QT</t>
+          <t>CoroMill 216 (R216-20T3)</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M12</t>
+          <t>METRIC_THREAD:M10</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>ISCAR_BCR_D250</t>
+          <t>COR_R216:20H</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -891,21 +925,21 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="Z4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>17.8</v>
+      </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>ISC_BCR_D250</t>
+          <t>COR_R216-20T3_H</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -914,40 +948,48 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2020 / Главный каталог</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RCF-20-10R-M10-2T</t>
+          <t>R216-16T08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>CoroMillⓇ 216 ball nose milling cutter</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12.8</v>
+      </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>25</v>
+      </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
@@ -955,17 +997,21 @@
       <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>85</v>
+      </c>
+      <c r="N5" t="n">
+        <v>12700</v>
+      </c>
       <c r="O5" t="n">
-        <v>0.09</v>
+        <v>0.109</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ZCEW100CE/ZCEW100SE</t>
+          <t>CoroMill 216 (R216-1603)</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -979,12 +1025,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M10</t>
+          <t>METRIC_THREAD:M8</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>DER_ZCEW100H</t>
+          <t>COR_R216:16H</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -995,19 +1041,21 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>12.8</v>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>ZC10*_H</t>
+          <t>COR_R216-1603_H</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1016,14 +1064,20 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R216-12T08</t>
+          <t>R216-16EH16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1037,23 +1091,21 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="F6" t="n">
-        <v>12.8</v>
+        <v>15.5</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>18.3</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>25</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
@@ -1068,33 +1120,33 @@
         <v>12700</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>14.4</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>CoroMill 216 (R216-1202)</t>
+          <t>CoroMill 216 (R216-1603)</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M8</t>
+          <t>METRIC_EH:16</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>COR_R216:12H</t>
+          <t>COR_R216:16H</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1105,16 +1157,16 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
-        <v>12.8</v>
+        <v>15.5</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>COR_R216-1202_H</t>
+          <t>COR_R216-1603_H</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1131,6 +1183,12 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
